--- a/data/trans_orig/P41D_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P41D_2023-Provincia-trans_orig.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W31"/>
+  <dimension ref="A1:W28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si con respecto a la última vez que lo intentaron se quedó embarazada en 2023</t>
+          <t>Población según si con respecto a la última vez que lo intentaron se quedó embarazada en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -710,7 +710,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -755,12 +755,12 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1141</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -790,37 +790,37 @@
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1142</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2595</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>43,99%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100,0%</t>
         </is>
       </c>
     </row>
@@ -833,12 +833,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1453</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -903,37 +903,37 @@
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1453</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2595</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>56,01%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100,0%</t>
         </is>
       </c>
     </row>
@@ -946,114 +946,114 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1453</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1453</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1453</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1141</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1141</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1141</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2595</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2595</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2595</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1121</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,82 +1088,82 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1142</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2595</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1181,17 +1181,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1453</t>
+          <t>1207</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1453</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,82 +1201,82 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2107</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1453</t>
+          <t>3314</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2595</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>56,01%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1453</t>
+          <t>1207</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1453</t>
+          <t>1207</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1453</t>
+          <t>1207</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1324,22 +1324,22 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>2107</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>2107</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>2107</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1359,22 +1359,22 @@
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2595</t>
+          <t>3314</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2595</t>
+          <t>3314</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2595</t>
+          <t>3314</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1396,7 +1396,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Granada</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>931</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>936</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1201</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1519,22 +1519,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1207</t>
+          <t>4361</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1207</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,32 +1544,32 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2107</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2107</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,17 +1594,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>3314</t>
+          <t>6001</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2113</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>3314</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1632,22 +1632,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1207</t>
+          <t>4361</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1207</t>
+          <t>4361</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1207</t>
+          <t>4361</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1667,22 +1667,22 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2107</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2107</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2107</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>3314</t>
+          <t>6001</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3314</t>
+          <t>6001</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3314</t>
+          <t>6001</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1739,7 +1739,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Granada</t>
+          <t>Huelva</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2483</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>934</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2175</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1862,107 +1862,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>694</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>4361</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>1878</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4361</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1276</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>43,07%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>1640</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>706</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>1640</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>43,07%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>6001</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>3826</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>6001</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1975,92 +1975,92 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>694</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>694</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>694</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>4361</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>4361</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>4361</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>1640</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>1640</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>1640</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>6001</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>6001</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>6001</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2082,7 +2082,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Huelva</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -2097,102 +2097,102 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>535</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>783</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>1416</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>55,32%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>449</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>783</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>1416</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>55,32%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>726</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>100,0%</t>
         </is>
       </c>
     </row>
@@ -2205,107 +2205,107 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>694</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>694</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>1416</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>44,68%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>22,85%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>582</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>582</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>1416</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>44,68%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>22,85%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>1276</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>550</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>1276</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>43,07%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>1416</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>1416</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>1416</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>1416</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>1416</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>1416</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>Jaén</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2435,107 +2435,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>783</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>1416</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>55,32%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>1307</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>4373</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>24,6%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>783</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>1416</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>55,32%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>82,3%</t>
         </is>
       </c>
     </row>
@@ -2548,102 +2548,102 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2225</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>62,99%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>1782</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1416</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>4007</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>885</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1416</t>
+          <t>5314</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>75,4%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2661,37 +2661,37 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1416</t>
+          <t>1782</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1416</t>
+          <t>1782</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1416</t>
+          <t>1782</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2731,22 +2731,22 @@
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1416</t>
+          <t>5314</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1416</t>
+          <t>5314</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1416</t>
+          <t>5314</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2768,7 +2768,7 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>Málaga</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -2778,107 +2778,107 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>1646</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>2875</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>57,26%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>1014</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>1646</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>3798</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>33,35%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>1307</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>4418</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>24,6%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>76,95%</t>
         </is>
       </c>
     </row>
@@ -2896,97 +2896,97 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2061</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>62,99%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>1229</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>2875</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>42,74%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>1782</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>768</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>1782</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>43,07%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>4007</t>
+          <t>3290</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>1138</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5314</t>
+          <t>4936</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>66,65%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>2061</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>2061</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>2061</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>3532</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>3532</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>3532</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1782</t>
+          <t>2875</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1782</t>
+          <t>2875</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1782</t>
+          <t>2875</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>5314</t>
+          <t>4936</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>5314</t>
+          <t>4936</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>5314</t>
+          <t>4936</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3111,7 +3111,7 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -3121,12 +3121,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -3136,92 +3136,92 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1173</t>
+          <t>5732</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
+          <t>9,82%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1646</t>
+          <t>3571</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1071</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2875</t>
+          <t>6917</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>57,26%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>59,91%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1646</t>
+          <t>4879</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1830</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3798</t>
+          <t>10417</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>41,91%</t>
         </is>
       </c>
     </row>
@@ -3234,107 +3234,107 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2061</t>
+          <t>12001</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>7576</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2061</t>
+          <t>13308</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
+          <t>90,18%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>56,92%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>43,07%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1229</t>
+          <t>7973</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4627</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2875</t>
+          <t>10473</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>69,07%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>3290</t>
+          <t>19974</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1138</t>
+          <t>14436</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4936</t>
+          <t>23023</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>80,37%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>58,09%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>92,64%</t>
         </is>
       </c>
     </row>
@@ -3347,22 +3347,22 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2061</t>
+          <t>13308</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2061</t>
+          <t>13308</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2061</t>
+          <t>13308</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3382,22 +3382,22 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2875</t>
+          <t>11544</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2875</t>
+          <t>11544</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2875</t>
+          <t>11544</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>24</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>4936</t>
+          <t>24853</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>4936</t>
+          <t>24853</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>4936</t>
+          <t>24853</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3452,364 +3452,20 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>1307</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>6071</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>9,82%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>45,62%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>3571</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>986</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>7024</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>30,93%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>8,55%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>60,85%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>4879</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>1816</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>10213</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>19,63%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>7,31%</t>
-        </is>
-      </c>
-      <c r="W28" s="2" t="inlineStr">
-        <is>
-          <t>41,09%</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="n"/>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>12001</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>7237</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>13308</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>90,18%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>54,38%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>7973</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>4520</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>10558</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>69,07%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>39,15%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>91,45%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>19974</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>14640</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>23037</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>80,37%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>58,91%</t>
-        </is>
-      </c>
-      <c r="W29" s="2" t="inlineStr">
-        <is>
-          <t>92,69%</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="n"/>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>13308</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>13308</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>13308</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>11544</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>11544</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>11544</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>24853</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>24853</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>24853</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="12">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A25:A27"/>
-    <mergeCell ref="A28:A30"/>
     <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="Q1:W1"/>

--- a/data/trans_orig/P41D_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P41D_2023-Provincia-trans_orig.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>1093</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1142</t>
+          <t>1093</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2595</t>
+          <t>2550</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1453</t>
+          <t>1457</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1453</t>
+          <t>1457</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2595</t>
+          <t>2550</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>56,01%</t>
+          <t>57,13%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1453</t>
+          <t>1457</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1453</t>
+          <t>1457</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1453</t>
+          <t>1457</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>1093</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>1093</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>1093</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>2595</t>
+          <t>2550</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2595</t>
+          <t>2550</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>2595</t>
+          <t>2550</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1207</t>
+          <t>1178</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2107</t>
+          <t>2110</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3314</t>
+          <t>3288</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1207</t>
+          <t>1178</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1207</t>
+          <t>1178</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1207</t>
+          <t>1178</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2107</t>
+          <t>2110</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2107</t>
+          <t>2110</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2107</t>
+          <t>2110</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>3314</t>
+          <t>3288</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3314</t>
+          <t>3288</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>3314</t>
+          <t>3288</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4361</t>
+          <t>4922</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1640</t>
+          <t>1670</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>6001</t>
+          <t>6592</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4361</t>
+          <t>4922</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4361</t>
+          <t>4922</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4361</t>
+          <t>4922</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1640</t>
+          <t>1670</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1640</t>
+          <t>1670</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1640</t>
+          <t>1670</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>6001</t>
+          <t>6592</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6001</t>
+          <t>6592</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6001</t>
+          <t>6592</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>780</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>663</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>1443</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>780</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>780</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>780</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>663</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>663</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>663</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>1443</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>1443</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>1443</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>783</t>
+          <t>771</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1416</t>
+          <t>1419</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>55,32%</t>
+          <t>54,34%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>783</t>
+          <t>771</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -2177,12 +2177,12 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1416</t>
+          <t>1419</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>55,32%</t>
+          <t>54,34%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>648</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2255,12 +2255,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1416</t>
+          <t>1419</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>45,66%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>648</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -2290,12 +2290,12 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1416</t>
+          <t>1419</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>45,66%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1416</t>
+          <t>1419</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1416</t>
+          <t>1419</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1416</t>
+          <t>1419</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1416</t>
+          <t>1419</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1416</t>
+          <t>1419</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1416</t>
+          <t>1419</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>3512</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4373</t>
+          <t>4442</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>83,55%</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2250</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>3512</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>62,99%</t>
+          <t>64,06%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1782</t>
+          <t>1805</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2623,27 +2623,27 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>4007</t>
+          <t>4055</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>880</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5314</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>3512</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>3512</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>3512</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1782</t>
+          <t>1805</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1782</t>
+          <t>1805</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1782</t>
+          <t>1805</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>5314</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>5314</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>5314</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1646</t>
+          <t>1767</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2875</t>
+          <t>3120</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>57,26%</t>
+          <t>56,63%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1646</t>
+          <t>1767</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3798</t>
+          <t>4163</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>76,51%</t>
         </is>
       </c>
     </row>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2061</t>
+          <t>2322</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1229</t>
+          <t>1353</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2875</t>
+          <t>3120</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>43,37%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -2966,27 +2966,27 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>3290</t>
+          <t>3674</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1138</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4936</t>
+          <t>5441</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>67,53%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2061</t>
+          <t>2322</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2061</t>
+          <t>2322</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2061</t>
+          <t>2322</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2875</t>
+          <t>3120</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2875</t>
+          <t>3120</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2875</t>
+          <t>3120</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>4936</t>
+          <t>5441</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4936</t>
+          <t>5441</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>4936</t>
+          <t>5441</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,7 +3126,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5732</t>
+          <t>5855</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>41,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>3571</t>
+          <t>3631</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1071</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6917</t>
+          <t>7250</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>61,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>4879</t>
+          <t>4893</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1830</t>
+          <t>1765</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>10417</t>
+          <t>10568</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>40,57%</t>
         </is>
       </c>
     </row>
@@ -3239,27 +3239,27 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>12001</t>
+          <t>12908</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>7576</t>
+          <t>8315</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>13308</t>
+          <t>14170</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>58,68%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>7973</t>
+          <t>8249</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>4627</t>
+          <t>4630</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>10473</t>
+          <t>10868</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>69,44%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>38,98%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>19974</t>
+          <t>21157</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>14436</t>
+          <t>15482</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>23023</t>
+          <t>24285</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>59,43%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>93,23%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>13308</t>
+          <t>14170</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>13308</t>
+          <t>14170</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>13308</t>
+          <t>14170</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>11544</t>
+          <t>11880</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>11544</t>
+          <t>11880</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>11544</t>
+          <t>11880</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>24853</t>
+          <t>26050</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>24853</t>
+          <t>26050</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>24853</t>
+          <t>26050</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
